--- a/artfynd/A 27619-2022 artfynd.xlsx
+++ b/artfynd/A 27619-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27619-2022 artfynd.xlsx
+++ b/artfynd/A 27619-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95158399</v>
+        <v>95158439</v>
       </c>
       <c r="B2" t="n">
-        <v>29897</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,28 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>200985</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415327.0698013961</v>
+        <v>415253</v>
       </c>
       <c r="R2" t="n">
-        <v>6257109.323971029</v>
+        <v>6257316</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +747,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95158426</v>
+        <v>105421174</v>
       </c>
       <c r="B3" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,25 +805,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Misterhult, Sm</t>
+          <t>Johansdal, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415258.9103634532</v>
+        <v>414909</v>
       </c>
       <c r="R3" t="n">
-        <v>6257218.46990944</v>
+        <v>6257278</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +858,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På åker vid E4.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,34 +887,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95158439</v>
+        <v>95158681</v>
       </c>
       <c r="B4" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,27 +916,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415252.5399110366</v>
+        <v>415111</v>
       </c>
       <c r="R4" t="n">
-        <v>6257315.323509385</v>
+        <v>6256926</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,28 +977,17 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,6 +1003,212 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>95158399</v>
+      </c>
+      <c r="B5" t="n">
+        <v>30288</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>200985</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lasius fuliginosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Misterhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>415327</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6257109</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95158426</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Misterhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>415258</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6257218</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27619-2022 artfynd.xlsx
+++ b/artfynd/A 27619-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95158439</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105421174</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95158681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95158399</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,8 +1234,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95158426</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>